--- a/site/Template-Integrations-Configurations-Reference-Guide/headings.xlsx
+++ b/site/Template-Integrations-Configurations-Reference-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,51 +1365,51 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Log Name</t>
+          <t>Execution</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>h_01KS22AR3XG7BHQP3DD64SR6AX</t>
+          <t>h_01K58J992H41YFQ84G7R14SH7J</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KS22AR3XG7BHQP3DD64SR6AX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58J992H41YFQ84G7R14SH7J</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Incremental Mode</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>h_01K58J992H41YFQ84G7R14SH7J</t>
+          <t>h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58J992H41YFQ84G7R14SH7J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Incremental Mode</t>
+          <t>Incremental Mode Timestamp</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1419,19 +1419,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
+          <t>h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KKTYBF06CSBK5A2AJN3HWFXP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Incremental Mode Timestamp</t>
+          <t>Report Only</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
+          <t>h_01KKTY7RFXJK2DWK3DRV6GT4KG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KKTYBN3BW5P8S6E41R2HRG7T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KKTY7RFXJK2DWK3DRV6GT4KG</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Report Only</t>
+          <t>Allow Creation of Inactive Users</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1463,19 +1463,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>h_01KKTY7RFXJK2DWK3DRV6GT4KG</t>
+          <t>h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KKTY7RFXJK2DWK3DRV6GT4KG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Allow Creation of Inactive Users</t>
+          <t>Import Limit</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1485,19 +1485,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
+          <t>h_01K58JHXX6Z2HTAV55K7M925WX</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAPMJYJ6QYXJC8FJ5K9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58JHXX6Z2HTAV55K7M925WX</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Import Limit</t>
+          <t>Update Limit</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1507,19 +1507,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>h_01K58JHXX6Z2HTAV55K7M925WX</t>
+          <t>h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58JHXX6Z2HTAV55K7M925WX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Update Limit</t>
+          <t>Source Caching</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1529,19 +1529,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
+          <t>h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58JJ1N5B2A0FGEAPCZFYZ01</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Source Caching</t>
+          <t>Target Caching</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1551,63 +1551,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
+          <t>h_01K58XFVAP0BBF0GPYFKGANTV8</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58JJR8CCD94D1FZZ98WV2Z4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAP0BBF0GPYFKGANTV8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Target Caching</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>h_01K58XFVAP0BBF0GPYFKGANTV8</t>
+          <t>h_01K58M5M642N07HGFF4BGYYJSB</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAP0BBF0GPYFKGANTV8</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58M5M642N07HGFF4BGYYJSB</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Report Mode</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>h_01K58M5M642N07HGFF4BGYYJSB</t>
+          <t>01K58M5YKDTY2D8NQSS0D522RH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58M5M642N07HGFF4BGYYJSB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#01K58M5YKDTY2D8NQSS0D522RH</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Report Mode</t>
+          <t>Email From Address</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01K58M5YKDTY2D8NQSS0D522RH</t>
+          <t>01K58M5YKE0TB613KCAN1XYP4Q</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#01K58M5YKDTY2D8NQSS0D522RH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#01K58M5YKE0TB613KCAN1XYP4Q</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Email From Address</t>
+          <t>Send Reports</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1639,19 +1639,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>01K58M5YKE0TB613KCAN1XYP4Q</t>
+          <t>h_01K58XFVAQQGFA75V649HTX2Q0</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#01K58M5YKE0TB613KCAN1XYP4Q</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQQGFA75V649HTX2Q0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Send Reports</t>
+          <t>To</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1661,19 +1661,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQQGFA75V649HTX2Q0</t>
+          <t>h_01K58XFVAQ87D29WZXH2JRSV6E</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQQGFA75V649HTX2Q0</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQ87D29WZXH2JRSV6E</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>To</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1683,19 +1683,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQ87D29WZXH2JRSV6E</t>
+          <t>h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQ87D29WZXH2JRSV6E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Subject</t>
+          <t>Send On</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,19 +1705,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
+          <t>h_01K58XFVAQZ34103Z4HBTFE29B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQDNPXC5FHD2J8ZXME</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQZ34103Z4HBTFE29B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Send On</t>
+          <t>Safeguard Email List</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1727,19 +1727,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQZ34103Z4HBTFE29B</t>
+          <t>h_01K58XFVAQXSSG0ZYG9STYC063</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQZ34103Z4HBTFE29B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQXSSG0ZYG9STYC063</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Safeguard Email List</t>
+          <t>Send Details</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1749,19 +1749,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQXSSG0ZYG9STYC063</t>
+          <t>h_01K58XFVAQVABFWM19KJXDKVFZ</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQXSSG0ZYG9STYC063</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQVABFWM19KJXDKVFZ</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Send Details</t>
+          <t>Send CSV Report</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1771,19 +1771,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQVABFWM19KJXDKVFZ</t>
+          <t>h_01K58XFVAQCGB6H2XZXN0KQ6MD</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQVABFWM19KJXDKVFZ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQCGB6H2XZXN0KQ6MD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Send CSV Report</t>
+          <t>Send XLSX Report</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1793,19 +1793,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>h_01K58XFVAQCGB6H2XZXN0KQ6MD</t>
+          <t>h_01KNNSH8YRG1KG2AHGP75G8SBN</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K58XFVAQCGB6H2XZXN0KQ6MD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KNNSH8YRG1KG2AHGP75G8SBN</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Send XLSX Report</t>
+          <t>Dashboard Insights Level</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1815,120 +1815,98 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>h_01KNNSH8YRG1KG2AHGP75G8SBN</t>
+          <t>h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KNNSH8YRG1KG2AHGP75G8SBN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dashboard Insights Level</t>
+          <t>Monitor Provisioning</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
+          <t>h_01KM272YSX744Y0S9Q181YBPRC</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KM274GVJ6BXEG2BQ609KGJ8J</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KM272YSX744Y0S9Q181YBPRC</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Monitor Provisioning</t>
+          <t>Enable Monitoring</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>h_01KM272YSX744Y0S9Q181YBPRC</t>
+          <t>h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KM272YSX744Y0S9Q181YBPRC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Enable Monitoring</t>
+          <t>Appendix</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
+          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KM27D94ZAM5HS7P7PKF36ZZ7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Appendix</t>
+          <t>Integration Execution Report in Excel Format</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
+          <t>h_01KS2285RT7WYFNV6MSFDBDZPG</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01K1X7GKQKGYQTTNQVH6GAFV18</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Integration Execution Report in Excel Format</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>h_01KS2285RT7WYFNV6MSFDBDZPG</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Template-Integrations-Configurations-Reference-Guide/#h_01KS2285RT7WYFNV6MSFDBDZPG</t>
         </is>
